--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110324</v>
+        <v>110330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110330</v>
+        <v>110332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110332</v>
+        <v>110333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110339</v>
+        <v>110343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110343</v>
+        <v>110345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110345</v>
+        <v>110347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110347</v>
+        <v>110360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110360</v>
+        <v>110362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110362</v>
+        <v>110367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98320</v>
+        <v>98323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110367</v>
+        <v>110389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98323</v>
+        <v>98333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110389</v>
+        <v>110390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110390</v>
+        <v>110395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110395</v>
+        <v>110398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110398</v>
+        <v>110404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>98347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110404</v>
+        <v>110405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110405</v>
+        <v>110417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110417</v>
+        <v>110418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110418</v>
+        <v>110421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98363</v>
+        <v>98364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 63716-2023 artfynd.xlsx
+++ b/artfynd/A 63716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956941</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956954</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136956939</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136956942</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136956951</v>
       </c>
       <c r="B6" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136956952</v>
       </c>
       <c r="B7" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136956957</v>
       </c>
       <c r="B8" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136956959</v>
       </c>
       <c r="B9" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136956960</v>
       </c>
       <c r="B10" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136956962</v>
       </c>
       <c r="B11" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136956963</v>
       </c>
       <c r="B12" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136956965</v>
       </c>
       <c r="B13" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136956938</v>
       </c>
       <c r="B14" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136956943</v>
       </c>
       <c r="B15" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>136956950</v>
       </c>
       <c r="B16" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136956955</v>
       </c>
       <c r="B17" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136956958</v>
       </c>
       <c r="B18" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136956961</v>
       </c>
       <c r="B19" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136956966</v>
       </c>
       <c r="B20" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136956953</v>
       </c>
       <c r="B21" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136956937</v>
       </c>
       <c r="B22" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136956964</v>
       </c>
       <c r="B23" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
